--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12193,7 +12193,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>Evidence Collection</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>
